--- a/data/trans_dic/IQ26A_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IQ26A_R2-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5,84%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,75%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3,75%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,35%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 11,47</t>
+          <t>2,29; 8,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 7,2</t>
+          <t>3,87; 12,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,63</t>
+          <t>2,17; 8,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 32,74</t>
+          <t>0,0; 24,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 8,87</t>
+          <t>2,84; 10,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 12,34</t>
+          <t>1,58; 7,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 8,41</t>
+          <t>1,51; 8,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,99</t>
+          <t>2,12; 33,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 7,98</t>
+          <t>3,09; 8,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 8,09</t>
+          <t>3,42; 8,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,57</t>
+          <t>2,21; 6,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 19,86</t>
+          <t>2,28; 21,32</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,55%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21,44%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>9,17%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>6,61%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>14,38%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>31,31%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>12,48%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,55%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,55%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 12,09</t>
+          <t>9,54; 16,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,57; 9,69</t>
+          <t>6,83; 12,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,09; 19,04</t>
+          <t>11,5; 18,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,82; 48,25</t>
+          <t>12,68; 35,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,06; 15,81</t>
+          <t>6,57; 12,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 12,6</t>
+          <t>4,38; 9,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,03; 18,75</t>
+          <t>11,01; 18,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,52; 30,91</t>
+          <t>16,74; 40,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,85; 13,21</t>
+          <t>8,88; 13,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,21; 10,4</t>
+          <t>6,27; 10,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,03; 17,3</t>
+          <t>11,97; 17,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,54; 35,36</t>
+          <t>16,95; 32,95</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10,37%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15,83%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22,49%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>13,29%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>13,85%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>15,59%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19,21%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,37%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15,83%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,75; 18,57</t>
+          <t>7,03; 15,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,52; 18,77</t>
+          <t>7,0; 15,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,59; 20,28</t>
+          <t>11,96; 20,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,7; 30,89</t>
+          <t>12,95; 34,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,64; 15,14</t>
+          <t>8,77; 18,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,04; 14,81</t>
+          <t>9,78; 18,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,21; 20,9</t>
+          <t>11,69; 20,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,59; 35,49</t>
+          <t>11,3; 32,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,04; 15,1</t>
+          <t>8,86; 15,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,67; 15,49</t>
+          <t>9,3; 15,7</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,98; 18,83</t>
+          <t>12,57; 18,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,98; 30,7</t>
+          <t>14,97; 30,11</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16,79%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16,51%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19,76%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16,58%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>23,39%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>17,69%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>21,22%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26,73%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16,79%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,76%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,83; 28,41</t>
+          <t>13,07; 21,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,4; 22,53</t>
+          <t>12,67; 21,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,25; 27,04</t>
+          <t>15,19; 26,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,59; 37,61</t>
+          <t>10,06; 25,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,19; 21,28</t>
+          <t>19,04; 29,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,37; 21,2</t>
+          <t>13,28; 22,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,17; 25,89</t>
+          <t>16,42; 27,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,24; 23,78</t>
+          <t>17,69; 37,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,91; 23,41</t>
+          <t>17,05; 23,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,72; 20,46</t>
+          <t>14,1; 20,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,19; 23,99</t>
+          <t>16,94; 23,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,93; 26,27</t>
+          <t>14,93; 27,24</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12,11%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11,07%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18,7%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>13,63%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>14,57%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24,22%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>12,11%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,38; 15,74</t>
+          <t>10,22; 14,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,63; 12,63</t>
+          <t>9,15; 13,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,6; 16,86</t>
+          <t>12,32; 16,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,56; 31,16</t>
+          <t>13,88; 23,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,17; 14,29</t>
+          <t>11,84; 15,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,27; 13,11</t>
+          <t>8,67; 12,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,47; 16,98</t>
+          <t>12,71; 16,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,39; 23,93</t>
+          <t>18,13; 30,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,49; 14,39</t>
+          <t>11,28; 14,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,46; 12,22</t>
+          <t>9,43; 12,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,05; 16,08</t>
+          <t>13,03; 16,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,0; 25,21</t>
+          <t>17,03; 25,11</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1514,37 +1514,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8321</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5309</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>5336</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4666</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4502</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5183</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8321</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5309</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>1573</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2074</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2522; 10480</t>
+          <t>2519; 9619</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1973; 8954</t>
+          <t>4592; 14328</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1505; 9168</t>
+          <t>2537; 9421</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>331; 4502</t>
+          <t>0; 2604</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2527; 9740</t>
+          <t>2593; 9998</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4633; 14628</t>
+          <t>1970; 9228</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2632; 9808</t>
+          <t>1818; 10151</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2638</t>
+          <t>270; 4254</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6353; 16057</t>
+          <t>6207; 16641</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7913; 19649</t>
+          <t>8312; 19936</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5410; 15546</t>
+          <t>5241; 15135</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>452; 5353</t>
+          <t>535; 5010</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>31675</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>25486</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37548</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8463</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>23217</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>15625</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>30282</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10751</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>31675</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25486</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37548</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8873</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19625</t>
+          <t>16819</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16489; 30603</t>
+          <t>24215; 41482</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10799; 22883</t>
+          <t>18235; 34324</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23346; 40082</t>
+          <t>29676; 47130</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6807; 16567</t>
+          <t>5007; 13865</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22983; 40123</t>
+          <t>16634; 31249</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17927; 33630</t>
+          <t>10355; 22786</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28454; 48382</t>
+          <t>23183; 39665</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5155; 13835</t>
+          <t>5124; 12387</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44856; 66961</t>
+          <t>45008; 67185</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31233; 52332</t>
+          <t>31557; 52330</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56389; 81068</t>
+          <t>56067; 81086</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13872; 27974</t>
+          <t>11879; 23087</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>14672</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>16591</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29749</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11983</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>16946</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>21665</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>29360</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7686</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>14672</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>16591</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>29749</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13015</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20701</t>
+          <t>19822</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11166; 23686</t>
+          <t>9942; 21385</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14889; 29359</t>
+          <t>11055; 23917</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21821; 38181</t>
+          <t>22476; 38920</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3880; 12360</t>
+          <t>6903; 18293</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9398; 21423</t>
+          <t>11191; 23801</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11124; 23390</t>
+          <t>15302; 29349</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22944; 39265</t>
+          <t>22005; 37684</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7038; 19847</t>
+          <t>4347; 12595</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>24331; 40623</t>
+          <t>23848; 40471</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30394; 48690</t>
+          <t>29241; 49350</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48823; 70818</t>
+          <t>47279; 71045</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13410; 29451</t>
+          <t>13730; 27624</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>34595</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29710</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34392</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12338</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>45220</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>30315</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>14310</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>34595</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>29710</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>34392</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11759</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26069</t>
+          <t>27083</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36416; 54939</t>
+          <t>26923; 43306</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22963; 38597</t>
+          <t>22799; 39266</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28066; 46714</t>
+          <t>26445; 45456</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9417; 20140</t>
+          <t>7489; 19249</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27175; 43848</t>
+          <t>36826; 56241</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22254; 38149</t>
+          <t>22760; 39247</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26399; 45060</t>
+          <t>28363; 46737</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7098; 18257</t>
+          <t>9955; 21056</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>67528; 93502</t>
+          <t>68110; 93762</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48185; 71871</t>
+          <t>49531; 71878</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59609; 83199</t>
+          <t>58745; 82999</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19458; 34234</t>
+          <t>19515; 35594</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>148</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>86126</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>80108</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>106996</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33286</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>90719</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>72270</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>100807</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>34308</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>86126</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>80108</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>106996</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34087</t>
+          <t>32512</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68395</t>
+          <t>65798</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>75760; 104758</t>
+          <t>72698; 102824</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>59395; 86929</t>
+          <t>66216; 94161</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>87132; 116586</t>
+          <t>90733; 122750</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26286; 44143</t>
+          <t>24706; 42485</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>72335; 101655</t>
+          <t>78806; 105613</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>67074; 94857</t>
+          <t>59649; 86380</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91825; 125082</t>
+          <t>87884; 117410</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25523; 45615</t>
+          <t>25021; 42385</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>158159; 198043</t>
+          <t>155289; 197327</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>133547; 172507</t>
+          <t>133112; 171127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>186417; 229676</t>
+          <t>186116; 232128</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>56479; 83764</t>
+          <t>53818; 79361</t>
         </is>
       </c>
     </row>
